--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anderlecht II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -856,7 +856,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -966,7 +966,7 @@
         <v>1.61</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46008.5</v>
+        <v>46008.52083333334</v>
       </c>
     </row>
     <row r="5">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>2.36</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,55 +1730,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,55 +1730,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>2.36</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>2.36</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,55 +1492,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>2.35</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,55 +1492,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>2.36</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,55 +1492,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.7</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>2.49</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>3.31</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>2.49</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>7.05</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
         <v>1.28</v>
@@ -1278,49 +1278,49 @@
         <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
         <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
         <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.49</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="P8" t="n">
         <v>2.7</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>1.84</v>
       </c>
       <c r="R8" t="n">
         <v>1.28</v>
@@ -1397,49 +1397,49 @@
         <v>3.18</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC8" t="n">
         <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.31</v>
+        <v>2.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.81</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="V10" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.95</v>
+        <v>3.31</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>3.81</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -915,13 +915,13 @@
         <v>3.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
         <v>1.42</v>
@@ -945,7 +945,7 @@
         <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
         <v>3</v>
@@ -954,16 +954,16 @@
         <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46008.52083333334</v>
@@ -1025,13 +1025,13 @@
         <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="P5" t="n">
         <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.44</v>
@@ -1040,37 +1040,37 @@
         <v>2.35</v>
       </c>
       <c r="T5" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB5" t="n">
         <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
         <v>2.1</v>
@@ -1079,10 +1079,10 @@
         <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46008.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.49</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.7</v>
       </c>
-      <c r="O7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.28</v>
@@ -1278,49 +1278,49 @@
         <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC7" t="n">
         <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>2.49</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>7.05</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.28</v>
@@ -1397,49 +1397,49 @@
         <v>3.18</v>
       </c>
       <c r="T8" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="V8" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
         <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
         <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2.16</v>
+        <v>3.81</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.83</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
         <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.95</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.2</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="AC10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.19</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.31</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.81</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.55</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
         <v>6.1</v>
@@ -1894,10 +1894,10 @@
         <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>2.4</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1064,7 +1064,7 @@
         <v>2.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
         <v>4.2</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1266,7 +1266,7 @@
         <v>7.05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
         <v>1.84</v>
@@ -1278,37 +1278,37 @@
         <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="V7" t="n">
         <v>5.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
         <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
         <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
         <v>1.81</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.49</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.81</v>
+        <v>2.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>4.83</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>2.16</v>
+        <v>3.81</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.83</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1742,10 +1742,10 @@
         <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
         <v>1.32</v>
@@ -1766,13 +1766,13 @@
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA11" t="n">
         <v>1.7</v>
@@ -1781,19 +1781,19 @@
         <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
         <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
         <v>1.38</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>7.05</v>
       </c>
       <c r="P6" t="n">
         <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V6" t="n">
-        <v>5.45</v>
+        <v>5.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
         <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>2.36</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>7.05</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
         <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V7" t="n">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
         <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2.16</v>
+        <v>3.81</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.83</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.81</v>
+        <v>2.16</v>
       </c>
       <c r="P10" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>4.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,76 +897,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>3.18</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
         <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46008.52083333334</v>
+        <v>46008.58333333334</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.75</v>
+        <v>6.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>1.41</v>
       </c>
       <c r="O5" t="n">
-        <v>2.25</v>
+        <v>7.05</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.75</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>2.35</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>5.15</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.5</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46008.58333333334</v>
+        <v>46008.66666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="O6" t="n">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N8" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46008.66666666666</v>
+        <v>46008.6875</v>
       </c>
     </row>
     <row r="9">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>3.81</v>
+        <v>3.48</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="R9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.26</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,313 +1730,75 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46008.6875</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Scotland Premiership</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Dundee United</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI12" s="3" t="n">
-        <v>46008.70833333334</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Mount Pleasant Academy FC</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,76 +897,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>3.18</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>2.64</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AG4" t="n">
         <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46008.58333333334</v>
+        <v>46008.52083333334</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.6</v>
+        <v>1.75</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>1.41</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>7.05</v>
+        <v>2.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>5.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>2.35</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>5.15</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46008.66666666666</v>
+        <v>46008.58333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="O8" t="n">
-        <v>3.81</v>
+        <v>7.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V8" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="W8" t="n">
         <v>1.14</v>
@@ -1412,37 +1412,37 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
         <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.76</v>
+        <v>1.13</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46008.6875</v>
+        <v>46008.66666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1504,10 +1504,10 @@
         <v>3.48</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R9" t="n">
         <v>1.32</v>
@@ -1528,13 +1528,13 @@
         <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
         <v>1.7</v>
@@ -1543,22 +1543,22 @@
         <v>2.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
         <v>2.26</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.83</v>
+        <v>2.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
         <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>1.31</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1689,116 +1689,354 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>46008.6875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Racing United</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="3" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>46008.70833333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>2.25</v>
@@ -1064,7 +1064,7 @@
         <v>2.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
         <v>4.2</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.13</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>7.05</v>
+        <v>6.75</v>
       </c>
       <c r="P8" t="n">
         <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
         <v>3.18</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U8" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
         <v>5.15</v>
@@ -1412,13 +1412,13 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
         <v>2.2</v>
@@ -1430,16 +1430,16 @@
         <v>1.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
         <v>1.13</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.25</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.64</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.35</v>
+        <v>2.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="P10" t="n">
         <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
         <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.14</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC10" t="n">
         <v>2.32</v>
@@ -1674,10 +1674,10 @@
         <v>2.38</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>2.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>2.33</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.88</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.28</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH11" t="n">
-        <v>2.15</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.57</v>
       </c>
-      <c r="M9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
-        <v>3.72</v>
+        <v>4.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>4.75</v>
       </c>
       <c r="O10" t="n">
-        <v>3.81</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>4.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
         <v>1.54</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH10" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="N11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.33</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="V11" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.88</v>
+        <v>4.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.68</v>
+        <v>2.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>1.35</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V6" t="n">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>7.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="P7" t="n">
         <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>5.45</v>
+        <v>5.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="N9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="P9" t="n">
         <v>2.33</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Q9" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.88</v>
+        <v>4.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.68</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>2.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3.81</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.45</v>
+        <v>3.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.74</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="n">
         <v>2.85</v>
       </c>
-      <c r="N2" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O2" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.7</v>
+        <v>4.43</v>
       </c>
       <c r="R2" t="n">
         <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
         <v>3.84</v>
@@ -698,10 +698,10 @@
         <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
         <v>2.88</v>
@@ -710,19 +710,19 @@
         <v>1.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AD2" t="n">
         <v>1.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
         <v>1.64</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.45</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>3.72</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>4.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.81</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>4.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
         <v>1.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH9" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4</v>
+        <v>3.72</v>
       </c>
       <c r="N10" t="n">
-        <v>4.75</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3.81</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.87</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA10" t="n">
         <v>1.54</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.16</v>
+        <v>1.74</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>2.25</v>
@@ -1055,10 +1055,10 @@
         <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
         <v>2.5</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>7.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="P8" t="n">
         <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="T8" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
-        <v>5.45</v>
+        <v>5.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="n">
         <v>4.4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.75</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.87</v>
+        <v>4.97</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
@@ -1516,34 +1516,34 @@
         <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD9" t="n">
         <v>1.67</v>
@@ -1552,10 +1552,10 @@
         <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
         <v>2.38</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>3.81</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
         <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.88</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.3</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V8" t="n">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -671,16 +671,16 @@
         <v>2.98</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
         <v>4.43</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
         <v>3.84</v>
@@ -704,13 +704,13 @@
         <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AB2" t="n">
         <v>1.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AD2" t="n">
         <v>1.07</v>
@@ -722,10 +722,10 @@
         <v>1.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -1263,64 +1263,64 @@
         <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>6.75</v>
+        <v>6.62</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
         <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
         <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -1391,22 +1391,22 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
         <v>2.32</v>
       </c>
       <c r="U8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
@@ -1415,28 +1415,28 @@
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
         <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
         <v>1.44</v>
@@ -1504,7 +1504,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
         <v>4.97</v>
@@ -1516,10 +1516,10 @@
         <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
         <v>4.55</v>
@@ -1546,7 +1546,7 @@
         <v>2.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="n">
         <v>1.53</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>4.45</v>
+        <v>5.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="M11" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>3.22</v>
+        <v>3.68</v>
       </c>
       <c r="P11" t="n">
         <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3</v>
+        <v>4.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1864,22 +1864,22 @@
         <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
         <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
@@ -1888,10 +1888,10 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
         <v>1.55</v>
@@ -1900,22 +1900,22 @@
         <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AD12" t="n">
         <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,76 +897,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.18</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
         <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46008.52083333334</v>
+        <v>46008.5</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>3.18</v>
       </c>
       <c r="O5" t="n">
-        <v>2.25</v>
+        <v>2.64</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46008.58333333334</v>
+        <v>46008.52083333334</v>
       </c>
     </row>
     <row r="6">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3.68</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.97</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="W9" t="n">
         <v>1.15</v>
@@ -1531,34 +1531,34 @@
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.98</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.68</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>4.97</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
         <v>1.15</v>
@@ -1769,34 +1769,34 @@
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.22</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>4.97</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>5.25</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
         <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.97</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -668,7 +668,7 @@
         <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="P2" t="n">
         <v>1.91</v>
@@ -725,7 +725,7 @@
         <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -906,34 +906,34 @@
         <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
         <v>1.52</v>
@@ -945,25 +945,25 @@
         <v>2.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
         <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46008.5</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N5" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="O5" t="n">
         <v>2.64</v>
@@ -1061,10 +1061,10 @@
         <v>3.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC5" t="n">
         <v>3</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>7.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>6.72</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>5.35</v>
+        <v>4.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>6.62</v>
+        <v>3.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="V9" t="n">
-        <v>4.45</v>
+        <v>5.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.18</v>
+        <v>2.51</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3.68</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.97</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
@@ -1650,34 +1650,34 @@
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.85</v>
+        <v>5.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.22</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>5.25</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1977,40 +1977,40 @@
         <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>6.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
         <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
         <v>1.55</v>
@@ -2019,22 +2019,22 @@
         <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
         <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG13" t="n">
         <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -659,55 +659,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>3.59</v>
       </c>
       <c r="O2" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
         <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.43</v>
+        <v>4.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="U2" t="n">
         <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AC2" t="n">
         <v>5.6</v>
@@ -716,16 +716,16 @@
         <v>1.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
         <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>2.48</v>
@@ -933,13 +933,13 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AA4" t="n">
         <v>2.5</v>
@@ -960,7 +960,7 @@
         <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AH4" t="n">
         <v>1.86</v>
@@ -1144,13 +1144,13 @@
         <v>1.35</v>
       </c>
       <c r="O6" t="n">
-        <v>6.72</v>
+        <v>6.78</v>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -1159,13 +1159,13 @@
         <v>3.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
@@ -1174,19 +1174,19 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
         <v>4.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AD6" t="n">
         <v>1.5</v>
@@ -1257,13 +1257,13 @@
         <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>2.38</v>
@@ -1272,19 +1272,19 @@
         <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
         <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
         <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
         <v>1.09</v>
@@ -1293,28 +1293,28 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
         <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AG7" t="n">
         <v>1.3</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="O9" t="n">
         <v>2.88</v>
@@ -1507,7 +1507,7 @@
         <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -1516,7 +1516,7 @@
         <v>3.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
         <v>1.52</v>
@@ -1531,34 +1531,34 @@
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
         <v>2.51</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG9" t="n">
         <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1611,55 +1611,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="O10" t="n">
-        <v>3.68</v>
+        <v>3.79</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
         <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.48</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AC10" t="n">
         <v>2.18</v>
@@ -1668,16 +1668,16 @@
         <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
         <v>2.6</v>
@@ -1754,10 +1754,10 @@
         <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
         <v>4.55</v>
@@ -1769,28 +1769,28 @@
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>2.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
         <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
         <v>1.22</v>
@@ -1968,67 +1968,67 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="O13" t="n">
-        <v>6.53</v>
+        <v>6.48</v>
       </c>
       <c r="P13" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB13" t="n">
         <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
         <v>1.2</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="N5" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="O5" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="P5" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
         <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="T5" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V5" t="n">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46008.52083333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>1.35</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>6.78</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
@@ -1177,31 +1177,31 @@
         <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P9" t="n">
         <v>2.6</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2.5</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.51</v>
+        <v>2.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH9" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>5.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6.48</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -659,31 +659,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.59</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.76</v>
+        <v>4.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="U2" t="n">
         <v>1.18</v>
@@ -698,10 +698,10 @@
         <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
         <v>2.78</v>
@@ -710,22 +710,22 @@
         <v>1.34</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.6</v>
+        <v>5.85</v>
       </c>
       <c r="AD2" t="n">
         <v>1.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG2" t="n">
         <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,40 +1373,40 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>6.78</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
@@ -1415,31 +1415,31 @@
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.33</v>
+        <v>2.42</v>
       </c>
       <c r="O9" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="V9" t="n">
-        <v>4.55</v>
+        <v>5.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
-        <v>3.79</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
         <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -1635,22 +1635,22 @@
         <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
         <v>5</v>
@@ -1659,25 +1659,25 @@
         <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.6</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>5.35</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.51</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6.48</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.78</v>
+        <v>5.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46008.5</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="M5" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="N5" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="O5" t="n">
         <v>2.69</v>
       </c>
       <c r="P5" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46008.52083333334</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="N9" t="n">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -1516,7 +1516,7 @@
         <v>3.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
         <v>1.52</v>
@@ -1528,7 +1528,7 @@
         <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.2</v>
@@ -1537,19 +1537,19 @@
         <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
         <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
         <v>2.3</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.6</v>
+        <v>2.98</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
         <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>2.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
@@ -1656,28 +1656,28 @@
         <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.79</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
         <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
         <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
         <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
         <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>6</v>
@@ -2013,7 +2013,7 @@
         <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
         <v>2.3</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>6.78</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
@@ -1296,31 +1296,31 @@
         <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.98</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
         <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
@@ -1656,28 +1656,28 @@
         <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
         <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="W11" t="n">
         <v>1.15</v>
@@ -1775,28 +1775,28 @@
         <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -668,22 +668,22 @@
         <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.49</v>
+        <v>4.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U2" t="n">
         <v>1.18</v>
@@ -695,7 +695,7 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.55</v>
@@ -716,16 +716,16 @@
         <v>1.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
         <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>2.25</v>
@@ -942,10 +942,10 @@
         <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
         <v>4.2</v>
@@ -1025,40 +1025,40 @@
         <v>3.09</v>
       </c>
       <c r="O5" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
         <v>1.81</v>
@@ -1067,7 +1067,7 @@
         <v>1.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
         <v>1.44</v>
@@ -1082,7 +1082,7 @@
         <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46008.52083333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>7.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="M9" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>5.35</v>
+        <v>4.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1629,31 +1629,31 @@
         <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.6</v>
@@ -1662,10 +1662,10 @@
         <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
         <v>1.53</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>4.45</v>
+        <v>5.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>3.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>4.35</v>
+        <v>5.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.26</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.15</v>
+        <v>3.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>5.55</v>
+        <v>4.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6.48</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,90 +523,25 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Over25</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Under25</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>FT_Odd_Over05</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over15</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under15</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over25</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -677,57 +612,18 @@
         <v>4.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>2.78</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF2" t="n">
         <v>1.53</v>
       </c>
-      <c r="AG2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AI2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>46008.375</v>
       </c>
     </row>
@@ -807,46 +703,7 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="3" t="n">
+      <c r="V3" s="3" t="n">
         <v>46008.41666666666</v>
       </c>
     </row>
@@ -915,57 +772,18 @@
         <v>5.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V4" t="n">
-        <v>9</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="V4" s="3" t="n">
         <v>46008.5</v>
       </c>
     </row>
@@ -1034,57 +852,18 @@
         <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.81</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="T5" t="n">
-        <v>2.39</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF5" t="n">
         <v>2.45</v>
       </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI5" s="3" t="n">
+      <c r="V5" s="3" t="n">
         <v>46008.52083333334</v>
       </c>
     </row>
@@ -1109,12 +888,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,75 +914,36 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>46008.66666666666</v>
       </c>
     </row>
@@ -1272,57 +1012,18 @@
         <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF7" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI7" s="3" t="n">
+      <c r="V7" s="3" t="n">
         <v>46008.66666666666</v>
       </c>
     </row>
@@ -1347,12 +1048,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,75 +1074,36 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V8" s="3" t="n">
         <v>46008.66666666666</v>
       </c>
     </row>
@@ -1510,57 +1172,18 @@
         <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF9" t="n">
         <v>2.5</v>
       </c>
-      <c r="AG9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI9" s="3" t="n">
+      <c r="V9" s="3" t="n">
         <v>46008.6875</v>
       </c>
     </row>
@@ -1585,12 +1208,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,75 +1234,36 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.26</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.41</v>
+        <v>1.53</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI10" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>46008.6875</v>
       </c>
     </row>
@@ -1704,12 +1288,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,75 +1314,36 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>3.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>3.66</v>
+        <v>2.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH11" t="n">
         <v>2.3</v>
       </c>
-      <c r="AI11" s="3" t="n">
+      <c r="V11" s="3" t="n">
         <v>46008.6875</v>
       </c>
     </row>
@@ -1867,57 +1412,18 @@
         <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF12" t="n">
         <v>2.05</v>
       </c>
-      <c r="AG12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI12" s="3" t="n">
+      <c r="V12" s="3" t="n">
         <v>46008.70833333334</v>
       </c>
     </row>
@@ -1997,46 +1503,7 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="3" t="n">
+      <c r="V13" s="3" t="n">
         <v>46008.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,25 +523,90 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over15</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under15</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_D</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_D</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -612,18 +677,57 @@
         <v>4.76</v>
       </c>
       <c r="R2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA2" t="n">
         <v>2.78</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AB2" t="n">
         <v>1.34</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AC2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE2" t="n">
         <v>2.32</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AF2" t="n">
         <v>1.53</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="AG2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>46008.375</v>
       </c>
     </row>
@@ -703,7 +807,46 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>46008.41666666666</v>
       </c>
     </row>
@@ -772,18 +915,57 @@
         <v>5.75</v>
       </c>
       <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.42</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AB4" t="n">
         <v>1.5</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AC4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE4" t="n">
         <v>2.1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AF4" t="n">
         <v>1.67</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="AG4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>46008.5</v>
       </c>
     </row>
@@ -852,18 +1034,57 @@
         <v>3.1</v>
       </c>
       <c r="R5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.81</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AB5" t="n">
         <v>1.89</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AC5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AF5" t="n">
         <v>2.45</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="AG5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>46008.52083333334</v>
       </c>
     </row>
@@ -888,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -914,36 +1135,75 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>2.02</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
       </c>
     </row>
@@ -1012,18 +1272,57 @@
         <v>1.75</v>
       </c>
       <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.6</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AB7" t="n">
         <v>2.2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AC7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.75</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AF7" t="n">
         <v>1.95</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="AG7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
       </c>
     </row>
@@ -1048,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1074,36 +1373,75 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
       </c>
     </row>
@@ -1172,18 +1510,57 @@
         <v>2.45</v>
       </c>
       <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.55</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AB9" t="n">
         <v>2.25</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AC9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.44</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AF9" t="n">
         <v>2.5</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="AG9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
       </c>
     </row>
@@ -1208,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1234,36 +1611,75 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>3.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V10" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
       </c>
     </row>
@@ -1288,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1314,36 +1730,75 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.26</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.02</v>
+        <v>3.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2.3</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
       </c>
     </row>
@@ -1412,18 +1867,57 @@
         <v>1.85</v>
       </c>
       <c r="R12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.55</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AC12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.73</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AF12" t="n">
         <v>2.05</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="AG12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
       </c>
     </row>
@@ -1503,7 +1997,46 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -668,28 +668,28 @@
         <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.76</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="U2" t="n">
         <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -704,10 +704,10 @@
         <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>5.85</v>
@@ -716,16 +716,16 @@
         <v>1.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -906,34 +906,34 @@
         <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="T4" t="n">
         <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
         <v>9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.52</v>
@@ -942,28 +942,28 @@
         <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC4" t="n">
         <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46008.5</v>
@@ -1052,7 +1052,7 @@
         <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
         <v>1.15</v>
@@ -1067,7 +1067,7 @@
         <v>1.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AD5" t="n">
         <v>1.44</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>4.9</v>
+        <v>5.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>6.77</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.98</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>2.03</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>4.97</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>5.55</v>
+        <v>4.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
-        <v>4.35</v>
+        <v>5.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6.48</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>2.83</v>
@@ -674,13 +674,13 @@
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R2" t="n">
         <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
         <v>3.92</v>
@@ -695,37 +695,37 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC2" t="n">
         <v>5.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
         <v>2.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
         <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.14</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46008.41666666666</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="M5" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>3.09</v>
+        <v>2.78</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="P5" t="n">
         <v>2.38</v>
@@ -1034,46 +1034,46 @@
         <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="T5" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
         <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
         <v>4.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
         <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AF5" t="n">
         <v>2.45</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>1.37</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>6.77</v>
       </c>
       <c r="P7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AC7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.3</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>6.77</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>2.03</v>
+        <v>2.93</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.97</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="V9" t="n">
-        <v>4.4</v>
+        <v>5.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
         <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
         <v>2.47</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
         <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="U10" t="n">
         <v>1.64</v>
@@ -1653,19 +1653,19 @@
         <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.75</v>
+        <v>5.01</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
         <v>1.45</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>2.02</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>5.23</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.15</v>
+        <v>3.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>5.65</v>
+        <v>4.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>6.48</v>
+        <v>5.71</v>
       </c>
       <c r="P13" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V13" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
         <v>1.1</v>
@@ -2007,34 +2007,34 @@
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
         <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB13" t="n">
         <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="M4" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.78</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
         <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46008.5</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="N6" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.61</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.37</v>
+        <v>2.39</v>
       </c>
       <c r="O7" t="n">
-        <v>6.77</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>4.9</v>
+        <v>5.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>6.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>1.37</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>6.77</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH9" t="n">
         <v>2.35</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="V10" t="n">
-        <v>4.65</v>
+        <v>5.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.01</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.23</v>
+        <v>2.47</v>
       </c>
       <c r="R11" t="n">
         <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="V11" t="n">
-        <v>4.35</v>
+        <v>4.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>5.01</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="P2" t="n">
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.75</v>
+        <v>4.97</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="T2" t="n">
         <v>3.92</v>
@@ -698,28 +698,28 @@
         <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>5.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE2" t="n">
         <v>2.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG2" t="n">
         <v>1.32</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.39</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>6.77</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>5.35</v>
+        <v>4.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.9</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>6.77</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1495,37 +1495,37 @@
         <v>1.53</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.23</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
         <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
@@ -1534,31 +1534,31 @@
         <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AE9" t="n">
         <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
         <v>1.31</v>
@@ -1638,43 +1638,43 @@
         <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="V10" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB10" t="n">
         <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
         <v>1.44</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O11" t="n">
         <v>3.6</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
         <v>4.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.01</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
         <v>2.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
         <v>1.45</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="N4" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Z4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA4" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
         <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46008.5</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="N5" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="O5" t="n">
-        <v>2.71</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AD5" t="n">
         <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46008.52083333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>7.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.18</v>
+        <v>6.77</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>5.35</v>
+        <v>4.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>6.77</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1537,10 +1537,10 @@
         <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
         <v>2.18</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1656,10 +1656,10 @@
         <v>3.94</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
         <v>2.63</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
         <v>3.6</v>
@@ -1775,10 +1775,10 @@
         <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>2.26</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>5.71</v>
+        <v>5.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W13" t="n">
         <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
         <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD13" t="n">
         <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
         <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>4.65</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>3.96</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
         <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -668,13 +668,13 @@
         <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.97</v>
+        <v>5.14</v>
       </c>
       <c r="R2" t="n">
         <v>1.61</v>
@@ -695,7 +695,7 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.55</v>
@@ -713,19 +713,19 @@
         <v>5.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -778,49 +778,49 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="N3" t="n">
         <v>1.09</v>
       </c>
       <c r="O3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
         <v>1.06</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AA3" t="n">
         <v>1.25</v>
@@ -835,16 +835,16 @@
         <v>2.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46008.41666666666</v>
@@ -906,34 +906,34 @@
         <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
         <v>2.35</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
         <v>1.52</v>
@@ -948,16 +948,16 @@
         <v>1.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
         <v>1.17</v>
@@ -1037,7 +1037,7 @@
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
         <v>2.7</v>
@@ -1046,13 +1046,13 @@
         <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
         <v>1.24</v>
@@ -1067,22 +1067,22 @@
         <v>1.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
         <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46008.52083333334</v>
@@ -1144,40 +1144,40 @@
         <v>1.35</v>
       </c>
       <c r="O6" t="n">
-        <v>6.77</v>
+        <v>4.94</v>
       </c>
       <c r="P6" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.6</v>
@@ -1186,7 +1186,7 @@
         <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AD6" t="n">
         <v>1.53</v>
@@ -1195,13 +1195,13 @@
         <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O7" t="n">
         <v>3.1</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.75</v>
-      </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.96</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>4.94</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.2</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>4.94</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.98</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
         <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
         <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.5</v>
       </c>
-      <c r="V10" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AG10" t="n">
         <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="n">
         <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.98</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
         <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -655,77 +655,77 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="P2" t="n">
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.14</v>
+        <v>4.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="S2" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="T2" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>8.9</v>
+        <v>17</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.85</v>
+        <v>7.1</v>
       </c>
       <c r="AD2" t="n">
         <v>1.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46008.375</v>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="N3" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.44</v>
@@ -802,46 +802,46 @@
         <v>4.33</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AH3" t="n">
         <v>1.04</v>
@@ -906,34 +906,34 @@
         <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.35</v>
+        <v>4.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.52</v>
@@ -948,16 +948,16 @@
         <v>1.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
         <v>1.17</v>
@@ -1025,22 +1025,22 @@
         <v>3.09</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U5" t="n">
         <v>1.4</v>
@@ -1049,10 +1049,10 @@
         <v>7.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
         <v>1.24</v>
@@ -1067,22 +1067,22 @@
         <v>1.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
         <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46008.52083333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>5.42</v>
       </c>
       <c r="P6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1269,7 +1269,7 @@
         <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
@@ -1293,7 +1293,7 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
         <v>4.4</v>
@@ -1314,13 +1314,13 @@
         <v>1.52</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AG7" t="n">
         <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.94</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="U8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.62</v>
       </c>
-      <c r="V8" t="n">
-        <v>5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.98</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.55</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AF9" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.32</v>
+        <v>2.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
         <v>4.8</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1742,16 +1742,16 @@
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>2.38</v>
@@ -1766,13 +1766,13 @@
         <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
         <v>1.7</v>
@@ -1781,22 +1781,22 @@
         <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
         <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -764,17 +764,17 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -893,62 +893,62 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
         <v>1.28</v>
       </c>
       <c r="V4" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="AD4" t="n">
         <v>1.2</v>
@@ -960,10 +960,10 @@
         <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46008.5</v>
@@ -999,90 +999,90 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="M5" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>3.09</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
         <v>1.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46008.52083333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>3.61</v>
       </c>
       <c r="N6" t="n">
-        <v>1.35</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>5.42</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>4.9</v>
+        <v>5.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.52</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.95</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.5</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.55</v>
       </c>
-      <c r="V7" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AB7" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="O8" t="n">
         <v>3.75</v>
@@ -1397,10 +1397,10 @@
         <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="V8" t="n">
         <v>5.9</v>
@@ -1409,31 +1409,31 @@
         <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
         <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
         <v>2.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AG8" t="n">
         <v>1.3</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="O9" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
         <v>1.55</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.98</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.55</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="M11" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>5.09</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="O13" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.29</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>7.17</v>
       </c>
       <c r="M6" t="n">
-        <v>3.61</v>
+        <v>4.45</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>1.38</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>4.94</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="U6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.5</v>
       </c>
-      <c r="V6" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.17</v>
+        <v>2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>4.45</v>
+        <v>3.61</v>
       </c>
       <c r="N7" t="n">
-        <v>1.38</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>4.94</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>4.95</v>
+        <v>5.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.03</v>
+        <v>2.42</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.75</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.72</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="N9" t="n">
-        <v>2.21</v>
+        <v>5.25</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
         <v>1.62</v>
@@ -1650,34 +1650,34 @@
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.7</v>
+        <v>5.09</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.29</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46008.70833333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.09</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.44</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AG13" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46008.70833333334</v>

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1228,19 +1228,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="M7" t="n">
-        <v>3.61</v>
+        <v>3.38</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
         <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>5.35</v>
+        <v>5.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>3.61</v>
       </c>
       <c r="N8" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>5.9</v>
+        <v>5.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,19 +1466,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1488,44 +1488,44 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.68</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>2.85</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="T9" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
@@ -1534,31 +1534,31 @@
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="N10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.75</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.2</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,19 +1704,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="M11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.5</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1951,20 +1951,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">

--- a/jogos_2025-12-17.xlsx
+++ b/jogos_2025-12-17.xlsx
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.17</v>
+        <v>3.12</v>
       </c>
       <c r="M6" t="n">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="N6" t="n">
-        <v>1.38</v>
+        <v>1.96</v>
       </c>
       <c r="O6" t="n">
-        <v>4.94</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="V6" t="n">
-        <v>4.95</v>
+        <v>5.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.75</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1228,25 +1228,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.12</v>
+        <v>7.17</v>
       </c>
       <c r="M7" t="n">
-        <v>3.38</v>
+        <v>4.45</v>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>4.94</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>5.9</v>
+        <v>4.95</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>2.75</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46008.66666666666</v>
@@ -1466,19 +1466,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="M9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.5</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46008.6875</v>
@@ -1585,66 +1585,66 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
         <v>6</v>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
@@ -1653,31 +1653,31 @@
         <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46008.6875</v>
@@ -1704,99 +1704,99 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.75</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.2</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46008.6875</v>
